--- a/output/casestudy_20260908.xlsx
+++ b/output/casestudy_20260908.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>11.57776699999999</v>
+        <v>13.96688559999984</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>11.00900980000006</v>
+        <v>12.82985370000006</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>8.02846129999989</v>
+        <v>7.3938705999999</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>11.77910550000001</v>
+        <v>12.11457590000009</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>11.74298180000005</v>
+        <v>13.5722765999999</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>8.924684500000012</v>
+        <v>10.19141839999975</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>12.19344969999997</v>
+        <v>12.41396170000007</v>
       </c>
     </row>
     <row r="9">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>11.01610380000011</v>
+        <v>13.4848763</v>
       </c>
     </row>
     <row r="10">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>16.43503350000015</v>
+        <v>17.76443709999967</v>
       </c>
     </row>
   </sheetData>
@@ -11663,7 +11663,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11.6 초</t>
+          <t>14.0 초</t>
         </is>
       </c>
     </row>
@@ -11675,7 +11675,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11.0 초</t>
+          <t>12.8 초</t>
         </is>
       </c>
     </row>
@@ -11687,7 +11687,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8.0 초</t>
+          <t>7.4 초</t>
         </is>
       </c>
     </row>
@@ -11699,7 +11699,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11.8 초</t>
+          <t>12.1 초</t>
         </is>
       </c>
     </row>
@@ -11711,7 +11711,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11.7 초</t>
+          <t>13.6 초</t>
         </is>
       </c>
     </row>
@@ -11723,7 +11723,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8.9 초</t>
+          <t>10.2 초</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12.2 초</t>
+          <t>12.4 초</t>
         </is>
       </c>
     </row>
@@ -11747,7 +11747,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11.0 초</t>
+          <t>13.5 초</t>
         </is>
       </c>
     </row>
@@ -11759,7 +11759,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16.4 초</t>
+          <t>17.8 초</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>106.3 초</t>
+          <t>117.7 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260908.xlsx
+++ b/output/casestudy_20260908.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>13.96688559999984</v>
+        <v>10.06429019999996</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>12.82985370000006</v>
+        <v>9.569857899999988</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7.3938705999999</v>
+        <v>6.890282800000932</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>12.11457590000009</v>
+        <v>11.07162240000071</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>13.5722765999999</v>
+        <v>11.19839040000079</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>10.19141839999975</v>
+        <v>9.344600599999467</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>12.41396170000007</v>
+        <v>10.87274620000062</v>
       </c>
     </row>
     <row r="9">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>13.4848763</v>
+        <v>10.40932939999948</v>
       </c>
     </row>
     <row r="10">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>17.76443709999967</v>
+        <v>14.55527799999982</v>
       </c>
     </row>
   </sheetData>
@@ -11663,7 +11663,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14.0 초</t>
+          <t>10.1 초</t>
         </is>
       </c>
     </row>
@@ -11675,7 +11675,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12.8 초</t>
+          <t>9.6 초</t>
         </is>
       </c>
     </row>
@@ -11687,7 +11687,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7.4 초</t>
+          <t>6.9 초</t>
         </is>
       </c>
     </row>
@@ -11699,7 +11699,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12.1 초</t>
+          <t>11.1 초</t>
         </is>
       </c>
     </row>
@@ -11711,7 +11711,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13.6 초</t>
+          <t>11.2 초</t>
         </is>
       </c>
     </row>
@@ -11723,7 +11723,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10.2 초</t>
+          <t>9.3 초</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12.4 초</t>
+          <t>10.9 초</t>
         </is>
       </c>
     </row>
@@ -11747,7 +11747,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13.5 초</t>
+          <t>10.4 초</t>
         </is>
       </c>
     </row>
@@ -11759,7 +11759,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>17.8 초</t>
+          <t>14.6 초</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>117.7 초</t>
+          <t>97.5 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260908.xlsx
+++ b/output/casestudy_20260908.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>10.06429019999996</v>
+        <v>11.22269919999962</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>9.569857899999988</v>
+        <v>12.54184489999898</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>6.890282800000932</v>
+        <v>8.119572999999946</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>11.07162240000071</v>
+        <v>11.88902919999964</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>11.19839040000079</v>
+        <v>13.14370009999948</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>9.344600599999467</v>
+        <v>11.37052330000006</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>10.87274620000062</v>
+        <v>14.97572159999982</v>
       </c>
     </row>
     <row r="9">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>10.40932939999948</v>
+        <v>14.31108570000106</v>
       </c>
     </row>
     <row r="10">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>14.55527799999982</v>
+        <v>19.06044380000094</v>
       </c>
     </row>
   </sheetData>
@@ -11663,7 +11663,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10.1 초</t>
+          <t>11.2 초</t>
         </is>
       </c>
     </row>
@@ -11675,7 +11675,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9.6 초</t>
+          <t>12.5 초</t>
         </is>
       </c>
     </row>
@@ -11687,7 +11687,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6.9 초</t>
+          <t>8.1 초</t>
         </is>
       </c>
     </row>
@@ -11699,7 +11699,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11.1 초</t>
+          <t>11.9 초</t>
         </is>
       </c>
     </row>
@@ -11711,7 +11711,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11.2 초</t>
+          <t>13.1 초</t>
         </is>
       </c>
     </row>
@@ -11723,7 +11723,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9.3 초</t>
+          <t>11.4 초</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10.9 초</t>
+          <t>15.0 초</t>
         </is>
       </c>
     </row>
@@ -11747,7 +11747,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10.4 초</t>
+          <t>14.3 초</t>
         </is>
       </c>
     </row>
@@ -11759,7 +11759,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14.6 초</t>
+          <t>19.1 초</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>97.5 초</t>
+          <t>120.8 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260908.xlsx
+++ b/output/casestudy_20260908.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>11.22269919999962</v>
+        <v>10.07129020000139</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>12.54184489999898</v>
+        <v>9.925646499999857</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>8.119572999999946</v>
+        <v>6.598585799998546</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>11.88902919999964</v>
+        <v>10.4217521999999</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>13.14370009999948</v>
+        <v>10.9649516999998</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>11.37052330000006</v>
+        <v>8.399847699998645</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>14.97572159999982</v>
+        <v>10.63424830000076</v>
       </c>
     </row>
     <row r="9">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>14.31108570000106</v>
+        <v>10.55434470000182</v>
       </c>
     </row>
     <row r="10">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>19.06044380000094</v>
+        <v>14.86924500000168</v>
       </c>
     </row>
   </sheetData>
@@ -11663,7 +11663,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11.2 초</t>
+          <t>10.1 초</t>
         </is>
       </c>
     </row>
@@ -11675,7 +11675,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12.5 초</t>
+          <t>9.9 초</t>
         </is>
       </c>
     </row>
@@ -11687,7 +11687,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8.1 초</t>
+          <t>6.6 초</t>
         </is>
       </c>
     </row>
@@ -11699,7 +11699,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11.9 초</t>
+          <t>10.4 초</t>
         </is>
       </c>
     </row>
@@ -11711,7 +11711,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13.1 초</t>
+          <t>11.0 초</t>
         </is>
       </c>
     </row>
@@ -11723,7 +11723,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11.4 초</t>
+          <t>8.4 초</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>15.0 초</t>
+          <t>10.6 초</t>
         </is>
       </c>
     </row>
@@ -11747,7 +11747,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14.3 초</t>
+          <t>10.6 초</t>
         </is>
       </c>
     </row>
@@ -11759,7 +11759,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19.1 초</t>
+          <t>14.9 초</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>120.8 초</t>
+          <t>96.0 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260908.xlsx
+++ b/output/casestudy_20260908.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>10.07129020000139</v>
+        <v>15.76208489999772</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>9.925646499999857</v>
+        <v>15.03522819999853</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>6.598585799998546</v>
+        <v>10.35003549999965</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>10.4217521999999</v>
+        <v>16.14192539999931</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>10.9649516999998</v>
+        <v>17.22135129999879</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>8.399847699998645</v>
+        <v>13.46611130000019</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>10.63424830000076</v>
+        <v>16.81059810000079</v>
       </c>
     </row>
     <row r="9">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>10.55434470000182</v>
+        <v>17.63210590000017</v>
       </c>
     </row>
     <row r="10">
@@ -960,7 +960,111 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>14.86924500000168</v>
+        <v>23.72985799999879</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>R2 용인 실측 산업갑Ⅱ</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>industrial_a_2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2025-08-28 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>476.02327</v>
+      </c>
+      <c r="E11" t="n">
+        <v>132.28</v>
+      </c>
+      <c r="F11" t="n">
+        <v>132</v>
+      </c>
+      <c r="G11" t="n">
+        <v>41.08229342532648</v>
+      </c>
+      <c r="H11" t="n">
+        <v>100.8144862191238</v>
+      </c>
+      <c r="I11" t="n">
+        <v>11275362.58064516</v>
+      </c>
+      <c r="J11" t="n">
+        <v>50479997.995</v>
+      </c>
+      <c r="K11" t="n">
+        <v>61755360.57564516</v>
+      </c>
+      <c r="L11" t="n">
+        <v>18.25811148302467</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>cache</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>13.14113899999938</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>R3 용인 실측 산업갑Ⅰ저압</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>industrial_a_1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025-08-28 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>476.02327</v>
+      </c>
+      <c r="E12" t="n">
+        <v>132.28</v>
+      </c>
+      <c r="F12" t="n">
+        <v>132</v>
+      </c>
+      <c r="G12" t="n">
+        <v>41.08229342532648</v>
+      </c>
+      <c r="H12" t="n">
+        <v>100.8144862191238</v>
+      </c>
+      <c r="I12" t="n">
+        <v>19314000</v>
+      </c>
+      <c r="J12" t="n">
+        <v>51187453.19000001</v>
+      </c>
+      <c r="K12" t="n">
+        <v>70501453.19000001</v>
+      </c>
+      <c r="L12" t="n">
+        <v>27.39517999430332</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>cache</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>10.91039380000075</v>
       </c>
     </row>
   </sheetData>
@@ -974,7 +1078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2182,13 +2286,269 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>R2 용인 실측 산업갑Ⅱ</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>132</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>500</v>
+      </c>
+      <c r="C39" t="n">
+        <v>653924.9987308802</v>
+      </c>
+      <c r="D39" t="n">
+        <v>28.80135248983531</v>
+      </c>
+      <c r="E39" t="n">
+        <v>465585.7548272483</v>
+      </c>
+      <c r="F39" t="n">
+        <v>120</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1245080.322580647</v>
+      </c>
+      <c r="H39" t="n">
+        <v>21535513.25811382</v>
+      </c>
+      <c r="I39" t="n">
+        <v>22780593.58069446</v>
+      </c>
+      <c r="J39" t="n">
+        <v>22780593.58069446</v>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1307849.99746176</v>
+      </c>
+      <c r="D40" t="n">
+        <v>15.68075433387349</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1102769.252304211</v>
+      </c>
+      <c r="F40" t="n">
+        <v>120</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1289900.322580647</v>
+      </c>
+      <c r="H40" t="n">
+        <v>23430388.49657076</v>
+      </c>
+      <c r="I40" t="n">
+        <v>24720288.8191514</v>
+      </c>
+      <c r="J40" t="n">
+        <v>24720288.8191514</v>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2615699.994923521</v>
+      </c>
+      <c r="D41" t="n">
+        <v>8.179882063646165</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2401738.820199978</v>
+      </c>
+      <c r="F41" t="n">
+        <v>120</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1289900.322580647</v>
+      </c>
+      <c r="H41" t="n">
+        <v>24389700.32065878</v>
+      </c>
+      <c r="I41" t="n">
+        <v>25679600.64323942</v>
+      </c>
+      <c r="J41" t="n">
+        <v>25679600.64323942</v>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>R3 용인 실측 산업갑Ⅰ저압</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>132</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>500</v>
+      </c>
+      <c r="C43" t="n">
+        <v>653924.9987308802</v>
+      </c>
+      <c r="D43" t="n">
+        <v>28.80135248983531</v>
+      </c>
+      <c r="E43" t="n">
+        <v>465585.7548272483</v>
+      </c>
+      <c r="F43" t="n">
+        <v>120</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>20294793.9666931</v>
+      </c>
+      <c r="I43" t="n">
+        <v>20294793.9666931</v>
+      </c>
+      <c r="J43" t="n">
+        <v>20294793.9666931</v>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1307849.99746176</v>
+      </c>
+      <c r="D44" t="n">
+        <v>15.68075433387349</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1102769.252304211</v>
+      </c>
+      <c r="F44" t="n">
+        <v>120</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>22092752.93526037</v>
+      </c>
+      <c r="I44" t="n">
+        <v>22092752.93526036</v>
+      </c>
+      <c r="J44" t="n">
+        <v>22092752.93526036</v>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C45" t="n">
+        <v>2615699.994923521</v>
+      </c>
+      <c r="D45" t="n">
+        <v>8.179882063646165</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2401738.820199978</v>
+      </c>
+      <c r="F45" t="n">
+        <v>120</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>23047468.70481</v>
+      </c>
+      <c r="I45" t="n">
+        <v>23047468.70481</v>
+      </c>
+      <c r="J45" t="n">
+        <v>23047468.70481</v>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="11">
     <mergeCell ref="A18:A21"/>
     <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A38:A41"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A34:A37"/>
     <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A42:A45"/>
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="A30:A33"/>
     <mergeCell ref="A10:A13"/>
@@ -2204,7 +2564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I190"/>
+  <dimension ref="A1:I232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7645,27 +8005,1231 @@
       </c>
       <c r="I190" t="inlineStr"/>
     </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>R2 용인 실측 산업갑Ⅱ</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>500</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>기본요금 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>1245080.322580647</v>
+      </c>
+      <c r="E191" t="n">
+        <v>925798.0645161308</v>
+      </c>
+      <c r="F191" t="n">
+        <v>1289900.322580647</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I191" t="n">
+        <v>28.22716233887535</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>전력량요금 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>21535513.25811382</v>
+      </c>
+      <c r="E192" t="n">
+        <v>19368241.32598845</v>
+      </c>
+      <c r="F192" t="n">
+        <v>23129035.83176755</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I192" t="n">
+        <v>16.26005741499038</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>절감액(원)</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>22189157.0273027</v>
+      </c>
+      <c r="E193" t="n">
+        <v>19798036.90969418</v>
+      </c>
+      <c r="F193" t="n">
+        <v>23779866.56983206</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I193" t="n">
+        <v>16.74454164174902</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>12개월 환산 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>22189157.0273027</v>
+      </c>
+      <c r="E194" t="n">
+        <v>19798036.90969418</v>
+      </c>
+      <c r="F194" t="n">
+        <v>23779866.56983207</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I194" t="n">
+        <v>16.74454164174903</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>요금적용전력(kW)</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>120</v>
+      </c>
+      <c r="E195" t="n">
+        <v>120</v>
+      </c>
+      <c r="F195" t="n">
+        <v>122</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="I195" t="n">
+        <v>1.639344262295082</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>발전량(kWh)</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>653924.9987308802</v>
+      </c>
+      <c r="E196" t="n">
+        <v>653917.3979531642</v>
+      </c>
+      <c r="F196" t="n">
+        <v>653931.4335780952</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I196" t="n">
+        <v>0.002146345046327881</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>회수기간(년)</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="B198" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>기본요금 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>2599907.419354839</v>
+      </c>
+      <c r="E198" t="n">
+        <v>2283572.258064518</v>
+      </c>
+      <c r="F198" t="n">
+        <v>2599907.419354839</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I198" t="n">
+        <v>12.16717022057729</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>전력량요금 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>22102770.12484275</v>
+      </c>
+      <c r="E199" t="n">
+        <v>19406700.11432061</v>
+      </c>
+      <c r="F199" t="n">
+        <v>23756425.05056709</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I199" t="n">
+        <v>18.30967802178909</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>절감액(원)</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>24147448.41387501</v>
+      </c>
+      <c r="E200" t="n">
+        <v>21183168.77288513</v>
+      </c>
+      <c r="F200" t="n">
+        <v>25801103.33959934</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I200" t="n">
+        <v>17.89820577024177</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>12개월 환산 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>24147448.413875</v>
+      </c>
+      <c r="E201" t="n">
+        <v>21183168.77288513</v>
+      </c>
+      <c r="F201" t="n">
+        <v>25801103.33959934</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I201" t="n">
+        <v>17.89820577024177</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>요금적용전력(kW)</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>120</v>
+      </c>
+      <c r="E202" t="n">
+        <v>120</v>
+      </c>
+      <c r="F202" t="n">
+        <v>122</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="I202" t="n">
+        <v>1.639344262295082</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>발전량(kWh)</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>1307849.99746176</v>
+      </c>
+      <c r="E203" t="n">
+        <v>1307834.795906328</v>
+      </c>
+      <c r="F203" t="n">
+        <v>1307862.86715619</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I203" t="n">
+        <v>0.002146345046327881</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>회수기간(년)</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="B205" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>기본요금 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>2599907.419354839</v>
+      </c>
+      <c r="E205" t="n">
+        <v>2283572.258064518</v>
+      </c>
+      <c r="F205" t="n">
+        <v>2599907.419354839</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I205" t="n">
+        <v>12.16717022057729</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>전력량요금 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>23105596.05380414</v>
+      </c>
+      <c r="E206" t="n">
+        <v>20240305.15024482</v>
+      </c>
+      <c r="F206" t="n">
+        <v>24434690.93852161</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I206" t="n">
+        <v>17.16570018761436</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>절감액(원)</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>25150274.34283639</v>
+      </c>
+      <c r="E207" t="n">
+        <v>21972035.28451838</v>
+      </c>
+      <c r="F207" t="n">
+        <v>26479369.22755386</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I207" t="n">
+        <v>17.02205934099533</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>12개월 환산 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>25150274.34283639</v>
+      </c>
+      <c r="E208" t="n">
+        <v>21972035.28451838</v>
+      </c>
+      <c r="F208" t="n">
+        <v>26479369.22755386</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I208" t="n">
+        <v>17.02205934099533</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>요금적용전력(kW)</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>120</v>
+      </c>
+      <c r="E209" t="n">
+        <v>120</v>
+      </c>
+      <c r="F209" t="n">
+        <v>122</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
+        <v>1.639344262295082</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>발전량(kWh)</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>2615699.994923521</v>
+      </c>
+      <c r="E210" t="n">
+        <v>2615669.591812657</v>
+      </c>
+      <c r="F210" t="n">
+        <v>2615725.734312381</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I210" t="n">
+        <v>0.002146345046327881</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>회수기간(년)</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>R3 용인 실측 산업갑Ⅰ저압</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>500</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>기본요금 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>0</v>
+      </c>
+      <c r="E212" t="n">
+        <v>0</v>
+      </c>
+      <c r="F212" t="n">
+        <v>0</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>전력량요금 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>20294793.9666931</v>
+      </c>
+      <c r="E213" t="n">
+        <v>18236372.92243502</v>
+      </c>
+      <c r="F213" t="n">
+        <v>21913030.74128586</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I213" t="n">
+        <v>16.77840852896599</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>절감액(원)</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>19155942.1080603</v>
+      </c>
+      <c r="E214" t="n">
+        <v>17310750.2163354</v>
+      </c>
+      <c r="F214" t="n">
+        <v>20676934.74128586</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
+        <v>16.27990109302402</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>12개월 환산 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>19155942.1080603</v>
+      </c>
+      <c r="E215" t="n">
+        <v>17310750.2163354</v>
+      </c>
+      <c r="F215" t="n">
+        <v>20676934.74128586</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I215" t="n">
+        <v>16.27990109302402</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>요금적용전력(kW)</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>120</v>
+      </c>
+      <c r="E216" t="n">
+        <v>120</v>
+      </c>
+      <c r="F216" t="n">
+        <v>122</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="I216" t="n">
+        <v>1.639344262295082</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>발전량(kWh)</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>653924.9987308802</v>
+      </c>
+      <c r="E217" t="n">
+        <v>653917.3979531642</v>
+      </c>
+      <c r="F217" t="n">
+        <v>653931.4335780952</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I217" t="n">
+        <v>0.002146345046327881</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>회수기간(년)</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="B219" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>기본요금 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>0</v>
+      </c>
+      <c r="E219" t="n">
+        <v>0</v>
+      </c>
+      <c r="F219" t="n">
+        <v>0</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>전력량요금 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>22092752.93526037</v>
+      </c>
+      <c r="E220" t="n">
+        <v>19592409.3476062</v>
+      </c>
+      <c r="F220" t="n">
+        <v>23782079.87861523</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I220" t="n">
+        <v>17.61692228935941</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>절감액(원)</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>20856656.93526036</v>
+      </c>
+      <c r="E221" t="n">
+        <v>18503171.43509091</v>
+      </c>
+      <c r="F221" t="n">
+        <v>22545983.87861522</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I221" t="n">
+        <v>17.93140838426173</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>12개월 환산 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>20856656.93526036</v>
+      </c>
+      <c r="E222" t="n">
+        <v>18503171.43509091</v>
+      </c>
+      <c r="F222" t="n">
+        <v>22545983.87861522</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I222" t="n">
+        <v>17.93140838426172</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>요금적용전력(kW)</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>120</v>
+      </c>
+      <c r="E223" t="n">
+        <v>120</v>
+      </c>
+      <c r="F223" t="n">
+        <v>122</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="I223" t="n">
+        <v>1.639344262295082</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>발전량(kWh)</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>1307849.99746176</v>
+      </c>
+      <c r="E224" t="n">
+        <v>1307834.795906328</v>
+      </c>
+      <c r="F224" t="n">
+        <v>1307862.86715619</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I224" t="n">
+        <v>0.002146345046327881</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>회수기간(년)</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="B226" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>기본요금 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>0</v>
+      </c>
+      <c r="E226" t="n">
+        <v>0</v>
+      </c>
+      <c r="F226" t="n">
+        <v>0</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>전력량요금 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>23047468.70481</v>
+      </c>
+      <c r="E227" t="n">
+        <v>20331228.83472877</v>
+      </c>
+      <c r="F227" t="n">
+        <v>24435407.17121959</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I227" t="n">
+        <v>16.79603007116976</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>절감액(원)</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>21811372.70481</v>
+      </c>
+      <c r="E228" t="n">
+        <v>19145894.39113829</v>
+      </c>
+      <c r="F228" t="n">
+        <v>23199311.17121959</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I228" t="n">
+        <v>17.4721428156447</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>12개월 환산 절감액(원)</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>21811372.70481</v>
+      </c>
+      <c r="E229" t="n">
+        <v>19145894.39113829</v>
+      </c>
+      <c r="F229" t="n">
+        <v>23199311.17121959</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I229" t="n">
+        <v>17.4721428156447</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>요금적용전력(kW)</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>120</v>
+      </c>
+      <c r="E230" t="n">
+        <v>120</v>
+      </c>
+      <c r="F230" t="n">
+        <v>122</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="I230" t="n">
+        <v>1.639344262295082</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>발전량(kWh)</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>2615699.994923521</v>
+      </c>
+      <c r="E231" t="n">
+        <v>2615669.591812657</v>
+      </c>
+      <c r="F231" t="n">
+        <v>2615725.734312381</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>첨예형</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>평탄형</t>
+        </is>
+      </c>
+      <c r="I231" t="n">
+        <v>0.002146345046327881</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>회수기간(년)</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="44">
     <mergeCell ref="A44:A64"/>
     <mergeCell ref="B86:B92"/>
+    <mergeCell ref="B58:B64"/>
     <mergeCell ref="B44:B50"/>
     <mergeCell ref="B9:B15"/>
     <mergeCell ref="B23:B29"/>
-    <mergeCell ref="A23:A43"/>
     <mergeCell ref="B107:B113"/>
     <mergeCell ref="B37:B43"/>
     <mergeCell ref="B177:B183"/>
     <mergeCell ref="B128:B134"/>
+    <mergeCell ref="B226:B232"/>
     <mergeCell ref="B65:B71"/>
     <mergeCell ref="A170:A190"/>
+    <mergeCell ref="B205:B211"/>
     <mergeCell ref="A107:A127"/>
     <mergeCell ref="B142:B148"/>
+    <mergeCell ref="A191:A211"/>
+    <mergeCell ref="B198:B204"/>
+    <mergeCell ref="A212:A232"/>
     <mergeCell ref="A128:A148"/>
+    <mergeCell ref="B30:B36"/>
     <mergeCell ref="B16:B22"/>
-    <mergeCell ref="B30:B36"/>
     <mergeCell ref="B114:B120"/>
     <mergeCell ref="B79:B85"/>
+    <mergeCell ref="B212:B218"/>
     <mergeCell ref="B163:B169"/>
     <mergeCell ref="B51:B57"/>
     <mergeCell ref="B135:B141"/>
@@ -7682,7 +9246,9 @@
     <mergeCell ref="B121:B127"/>
     <mergeCell ref="B2:B8"/>
     <mergeCell ref="B93:B99"/>
-    <mergeCell ref="B58:B64"/>
+    <mergeCell ref="A23:A43"/>
+    <mergeCell ref="B191:B197"/>
+    <mergeCell ref="B219:B225"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7694,7 +9260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8217,8 +9783,66 @@
         <v>0</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>R2 용인 실측 산업갑Ⅱ</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>62608643.63090323</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-853283.0552580655</v>
+      </c>
+      <c r="E30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>61755360.57564516</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>R3 용인 실측 산업갑Ⅰ저압</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>70501453.19000001</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A17:A19"/>
@@ -8228,6 +9852,7 @@
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A23:A25"/>
     <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A30:A31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8239,7 +9864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9276,14 +10901,236 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>R2 용인 실측 산업갑Ⅱ</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>7.1 선택요금 전환</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>II → II</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>7.2 계약전력 조정</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>계약 290 kW (실제 값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>7.4 역률 개선 (92→97%)</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>112753.6258064508</v>
+      </c>
+      <c r="D49" t="n">
+        <v>112753.6258064508</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>요금표와 약관만으로 확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>7.6 ESS</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>중간~낮음</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>최소 규격 미달 — 필요 출력 23.1 kW &lt; 상업용 최소 50 kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>7.3 경제성DR</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>거래 가능일 244일 · 등록 권장 28 kW · 연간 감축 5,882 kWh</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>R3 용인 실측 산업갑Ⅰ저압</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>7.1 선택요금 전환</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>single → single</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>7.2 계약전력 조정</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>10456200</v>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>계약 290 kW (실제 값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>7.4 역률 개선 (92→97%)</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>193140</v>
+      </c>
+      <c r="D54" t="n">
+        <v>193140</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>요금표와 약관만으로 확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>7.6 ESS</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>중간~낮음</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>성립하는 목표 없음 — 참고 지점 0개 중 절감액 0 이하 0개</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>7.3 경제성DR</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>거래 가능일 244일 · 등록 권장 28 kW · 연간 감축 5,882 kWh</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="11">
     <mergeCell ref="A22:A26"/>
     <mergeCell ref="A17:A21"/>
     <mergeCell ref="A12:A16"/>
     <mergeCell ref="A27:A31"/>
     <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A52:A56"/>
     <mergeCell ref="A42:A46"/>
+    <mergeCell ref="A47:A51"/>
     <mergeCell ref="A7:A11"/>
     <mergeCell ref="A37:A41"/>
     <mergeCell ref="A32:A36"/>
@@ -9298,7 +11145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D133"/>
+  <dimension ref="A1:D161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11513,12 +13360,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>교차</t>
+          <t>R2 용인 실측 산업갑Ⅱ</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>C1 오전 피크형 &gt; C2 오후 피크형 (요금적용전력 저감 폭)</t>
+          <t>PV 0 kWp 절감액이 정확히 0</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -11528,14 +13375,14 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>C1 95.0 kW vs C2 5.0 kW — C2 는 피크가 늦어 PV 가 깎은 뒤 저녁 슬롯이 새 최대가 된다</t>
+          <t>0.000000 원</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="B129" t="inlineStr">
         <is>
-          <t>C3 평탄형은 기본요금 절감이 거의 없다 (절감의 대부분이 전력량요금)</t>
+          <t>용량 증가 시 전력량요금 절감액 단조 증가</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -11545,14 +13392,14 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>기본요금 비중 C3 3.6% vs C1 10.2% (C3 저감 26.0 kW)</t>
+          <t>0 → 21,535,513 → 23,430,388 → 24,389,700</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="B130" t="inlineStr">
         <is>
-          <t>C5 겨울 피크형은 기본요금 절감이 매우 작다</t>
+          <t>기본요금 절감액 단조 증가 후 포화</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -11562,14 +13409,14 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>저감률 C5 0.29% vs C1 1.79% — 겨울 대상월의 피크가 07~09시·17~20시라 PV 가 닿지 않는다</t>
+          <t>증분 1,245,080 → 44,820 → 0</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="B131" t="inlineStr">
         <is>
-          <t>C6 야간 피크형: 요금적용전력 &lt; 관측 최대수요 (경부하 제외, 5.2 ①)</t>
+          <t>용량 증가 시 요금적용전력 단조 감소</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -11579,14 +13426,14 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>관측 10,920.6 kW vs 요금적용 3,604.0 kW (67.0% 낮다)</t>
+          <t>132.0 → 120.0 → 120.0 → 120.0</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="B132" t="inlineStr">
         <is>
-          <t>C6 야간 피크형: 하한이 요금적용전력을 붙들어 PV 가 한 칸도 못 내린다</t>
+          <t>감도 세 시나리오의 발전량이 ±1% 이내 (총량 보존)</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -11596,39 +13443,527 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>C6 저감 0.00 kW vs C1 95.00 kW — 경부하 최대라 대상 수요가 하한 3,603.8 kW 아래에 있다</t>
+          <t>최대 편차 0.002%</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="B133" t="inlineStr">
         <is>
+          <t>기준값이 범위 안에 있음</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>벗어난 지표 0건</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>상한 시나리오 기록 (단조성은 요구하지 않는다)</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>기본요금 절감액 상한: 평탄형</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>선택요금 전환 절감액 ≥ 0 (확정 계산)</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>0 원 · II → II</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>역률 개선 절감액 = 기본요금의 1.0% (감액 상한)</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>112,754 원 (기본요금 11,275,363 의 1.00%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>DR 거래 가능일이 전체 일수보다 적음 (토·일·공휴일 제외)</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>244 / 365일</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>ESS 성립하지 않으면 목표가 0 (없는 목표를 내지 않는다)</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>viable=False · 목표 0 kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>ESS 목표를 냈으면 절감액 &gt; 0</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>목표 0 kW · 절감액 —</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>ESS 목표 달성이면 실제 요금적용전력이 목표 이하</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>어긋난 점 0개 / 0개</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>ESS 절감액이 0 이하인 점에는 회수기간이 없다</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>어긋난 점 0개 / 0개</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>R3 용인 실측 산업갑Ⅰ저압</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>PV 0 kWp 절감액이 정확히 0</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>0.000000 원</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>용량 증가 시 전력량요금 절감액 단조 증가</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>0 → 20,294,794 → 22,092,753 → 23,047,469</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>기본요금 절감액 단조 증가 후 포화</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>증분 0 → 0 → 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>용량 증가 시 요금적용전력 단조 감소</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>132.0 → 120.0 → 120.0 → 120.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>감도 세 시나리오의 발전량이 ±1% 이내 (총량 보존)</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>최대 편차 0.002%</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>기준값이 범위 안에 있음</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>벗어난 지표 0건</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>상한 시나리오 기록 (단조성은 요구하지 않는다)</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>기본요금 절감액 상한: 평탄형</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>선택요금 전환 절감액 ≥ 0 (확정 계산)</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>0 원 · single → single</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>역률 개선 절감액 = 기본요금의 1.0% (감액 상한)</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>193,140 원 (기본요금 19,314,000 의 1.00%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>DR 거래 가능일이 전체 일수보다 적음 (토·일·공휴일 제외)</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>244 / 365일</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>ESS 성립하지 않으면 목표가 0 (없는 목표를 내지 않는다)</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>viable=False · 목표 0 kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>ESS 목표를 냈으면 절감액 &gt; 0</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>목표 0 kW · 절감액 —</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>ESS 목표 달성이면 실제 요금적용전력이 목표 이하</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>어긋난 점 0개 / 0개</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>ESS 절감액이 0 이하인 점에는 회수기간이 없다</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>어긋난 점 0개 / 0개</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>교차</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>C1 오전 피크형 &gt; C2 오후 피크형 (요금적용전력 저감 폭)</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>C1 95.0 kW vs C2 5.0 kW — C2 는 피크가 늦어 PV 가 깎은 뒤 저녁 슬롯이 새 최대가 된다</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>C3 평탄형은 기본요금 절감이 거의 없다 (절감의 대부분이 전력량요금)</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>기본요금 비중 C3 3.6% vs C1 10.2% (C3 저감 26.0 kW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>C5 겨울 피크형은 기본요금 절감이 매우 작다</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>저감률 C5 0.29% vs C1 1.79% — 겨울 대상월의 피크가 07~09시·17~20시라 PV 가 닿지 않는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>C6 야간 피크형: 요금적용전력 &lt; 관측 최대수요 (경부하 제외, 5.2 ①)</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>관측 10,920.6 kW vs 요금적용 3,604.0 kW (67.0% 낮다)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>C6 야간 피크형: 하한이 요금적용전력을 붙들어 PV 가 한 칸도 못 내린다</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>C6 저감 0.00 kW vs C1 95.00 kW — 경부하 최대라 대상 수요가 하한 3,603.8 kW 아래에 있다</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="inlineStr">
+        <is>
           <t>C4 산업용(을) 주말 할인이 PV 최성기와 겹쳐 전력량요금 절감 비율이 낮다</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
         <is>
           <t>C4 4.95% vs C1 5.44% (봄·가을 토·일·공휴일 11~14시 할인 구간의 단가가 이미 낮다)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
     <mergeCell ref="A30:A43"/>
     <mergeCell ref="A44:A57"/>
     <mergeCell ref="A16:A29"/>
     <mergeCell ref="A114:A127"/>
+    <mergeCell ref="A128:A141"/>
+    <mergeCell ref="A142:A155"/>
     <mergeCell ref="A100:A113"/>
     <mergeCell ref="A72:A85"/>
     <mergeCell ref="A86:A99"/>
     <mergeCell ref="A2:A15"/>
     <mergeCell ref="A58:A71"/>
-    <mergeCell ref="A128:A133"/>
+    <mergeCell ref="A156:A161"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11640,7 +13975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11663,7 +13998,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10.1 초</t>
+          <t>15.8 초</t>
         </is>
       </c>
     </row>
@@ -11675,7 +14010,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9.9 초</t>
+          <t>15.0 초</t>
         </is>
       </c>
     </row>
@@ -11687,7 +14022,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6.6 초</t>
+          <t>10.4 초</t>
         </is>
       </c>
     </row>
@@ -11699,7 +14034,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.4 초</t>
+          <t>16.1 초</t>
         </is>
       </c>
     </row>
@@ -11711,7 +14046,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11.0 초</t>
+          <t>17.2 초</t>
         </is>
       </c>
     </row>
@@ -11723,7 +14058,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8.4 초</t>
+          <t>13.5 초</t>
         </is>
       </c>
     </row>
@@ -11735,7 +14070,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10.6 초</t>
+          <t>16.8 초</t>
         </is>
       </c>
     </row>
@@ -11747,7 +14082,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10.6 초</t>
+          <t>17.6 초</t>
         </is>
       </c>
     </row>
@@ -11759,43 +14094,67 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14.9 초</t>
+          <t>23.7 초</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>전체 소요</t>
+          <t>R2 용인 실측 산업갑Ⅱ 소요</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>96.0 초</t>
+          <t>13.1 초</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>기상 취득 호출</t>
+          <t>R3 용인 실측 산업갑Ⅰ저압 소요</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0 회</t>
+          <t>10.9 초</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>전체 소요</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>182.1 초</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>기상 취득 호출</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0 회</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>기상 캐시 적중</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>9/9 (C1~C8 은 좌표·기간이 같아 첫 건만 취득한다. 실측은 따로 선다)</t>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>11/11 (C1~C8 은 좌표·기간이 같아 첫 건만 취득한다. 실측 R1~R3 도 서로 같아 그중 첫 건만 취득한다)</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260908.xlsx
+++ b/output/casestudy_20260908.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>15.76208489999772</v>
+        <v>10.7458086000006</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>15.03522819999853</v>
+        <v>11.46569060000184</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>10.35003549999965</v>
+        <v>7.855843400000595</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>16.14192539999931</v>
+        <v>12.09897619999902</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>17.22135129999879</v>
+        <v>11.86837970000124</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>13.46611130000019</v>
+        <v>10.97934379999788</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>16.81059810000079</v>
+        <v>13.63354229999823</v>
       </c>
     </row>
     <row r="9">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>17.63210590000017</v>
+        <v>14.16431209999791</v>
       </c>
     </row>
     <row r="10">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>23.72985799999879</v>
+        <v>17.9200353999986</v>
       </c>
     </row>
     <row r="11">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>13.14113899999938</v>
+        <v>9.084609000001365</v>
       </c>
     </row>
     <row r="12">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>10.91039380000075</v>
+        <v>7.661419600000954</v>
       </c>
     </row>
   </sheetData>
@@ -13998,7 +13998,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15.8 초</t>
+          <t>10.7 초</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15.0 초</t>
+          <t>11.5 초</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10.4 초</t>
+          <t>7.9 초</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16.1 초</t>
+          <t>12.1 초</t>
         </is>
       </c>
     </row>
@@ -14046,7 +14046,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17.2 초</t>
+          <t>11.9 초</t>
         </is>
       </c>
     </row>
@@ -14058,7 +14058,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13.5 초</t>
+          <t>11.0 초</t>
         </is>
       </c>
     </row>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16.8 초</t>
+          <t>13.6 초</t>
         </is>
       </c>
     </row>
@@ -14082,7 +14082,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>17.6 초</t>
+          <t>14.2 초</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>23.7 초</t>
+          <t>17.9 초</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13.1 초</t>
+          <t>9.1 초</t>
         </is>
       </c>
     </row>
@@ -14118,7 +14118,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10.9 초</t>
+          <t>7.7 초</t>
         </is>
       </c>
     </row>
@@ -14130,7 +14130,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>182.1 초</t>
+          <t>136.4 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260908.xlsx
+++ b/output/casestudy_20260908.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>10.7458086000006</v>
+        <v>11.9448521000013</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>11.46569060000184</v>
+        <v>11.65679319999981</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7.855843400000595</v>
+        <v>7.518661999998585</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>12.09897619999902</v>
+        <v>12.33852979999938</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>11.86837970000124</v>
+        <v>13.07490949999919</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>10.97934379999788</v>
+        <v>11.22078159999728</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>13.63354229999823</v>
+        <v>13.60031639999943</v>
       </c>
     </row>
     <row r="9">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>14.16431209999791</v>
+        <v>12.14657689999876</v>
       </c>
     </row>
     <row r="10">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>17.9200353999986</v>
+        <v>17.85023329999967</v>
       </c>
     </row>
     <row r="11">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>9.084609000001365</v>
+        <v>8.027737500000512</v>
       </c>
     </row>
     <row r="12">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>7.661419600000954</v>
+        <v>6.643039999999019</v>
       </c>
     </row>
   </sheetData>
@@ -13998,7 +13998,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10.7 초</t>
+          <t>11.9 초</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11.5 초</t>
+          <t>11.7 초</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7.9 초</t>
+          <t>7.5 초</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12.1 초</t>
+          <t>12.3 초</t>
         </is>
       </c>
     </row>
@@ -14046,7 +14046,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11.9 초</t>
+          <t>13.1 초</t>
         </is>
       </c>
     </row>
@@ -14058,7 +14058,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11.0 초</t>
+          <t>11.2 초</t>
         </is>
       </c>
     </row>
@@ -14082,7 +14082,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14.2 초</t>
+          <t>12.1 초</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>9.1 초</t>
+          <t>8.0 초</t>
         </is>
       </c>
     </row>
@@ -14118,7 +14118,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7.7 초</t>
+          <t>6.6 초</t>
         </is>
       </c>
     </row>
@@ -14130,7 +14130,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>136.4 초</t>
+          <t>134.5 초</t>
         </is>
       </c>
     </row>
